--- a/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>875</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>411</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>25168</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36726</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>41930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55849</t>
+          <t>56082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70811</t>
+          <t>70533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89367</t>
+          <t>88755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31707</t>
+          <t>31591</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29950</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40726</t>
+          <t>40672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65263</t>
+          <t>65350</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79413</t>
+          <t>79119</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32970</t>
+          <t>32798</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>40525</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>52267</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -4845,12 +4845,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>918</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>518</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>566</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>270</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>23472</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>31187</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>36859</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>90879</t>
+          <t>91000</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>111043</t>
+          <t>111003</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>61508</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>83244</t>
+          <t>83199</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>157716</t>
+          <t>158244</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>191387</t>
+          <t>192435</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>460</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>36181</t>
+          <t>36248</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>50952</t>
+          <t>51069</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>64945</t>
+          <t>64282</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>90622</t>
+          <t>90906</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>107353</t>
+          <t>106540</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26994</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>36179</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>49276</t>
+          <t>48530</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>61515</t>
+          <t>60707</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -8890,12 +8890,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>382</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -9003,12 +9003,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>415</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>386</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9455,12 +9455,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9470,82 +9470,82 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>7024</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>10722</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R81" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="S81" s="2" t="inlineStr">
-        <is>
-          <t>1766</t>
-        </is>
-      </c>
-      <c r="T81" s="2" t="inlineStr">
-        <is>
-          <t>9975</t>
-        </is>
-      </c>
-      <c r="U81" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="V81" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>19310</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>19911</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>32472</t>
+          <t>33741</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>17081</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>30187</t>
+          <t>30061</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>25468</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>46801</t>
+          <t>46630</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>26629</t>
+          <t>26887</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>47753</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>33597</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>62375</t>
+          <t>60293</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>64903</t>
+          <t>66135</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>99869</t>
+          <t>99516</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>236389</t>
+          <t>236932</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>272541</t>
+          <t>269341</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>260634</t>
+          <t>259784</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>294445</t>
+          <t>293464</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>504212</t>
+          <t>506638</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>556195</t>
+          <t>555525</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>998</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>366</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5557</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4072</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>797</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -946,82 +946,82 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>866</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2217</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>359</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1285,47 +1285,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6373</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4141</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>864</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>851</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1398,72 +1398,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3782</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9025</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5839</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -1511,72 +1511,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5584</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4701</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1624,72 +1624,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6470</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4260</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8578</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2266</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1737,72 +1737,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9268</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5559</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15026</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11915</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7703</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17690</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>12646</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>18183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21045</t>
+          <t>21914</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27836</t>
+          <t>30289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46135</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38899</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>52277</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>56,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>31097</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25168</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>36533</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>57,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41930</t>
+          <t>24254</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56082</t>
+          <t>37323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>80383</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70533</t>
+          <t>68326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88755</t>
+          <t>86098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -1963,74 +1963,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>54689</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>54689</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>54689</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>72528</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>72528</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>72528</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>178</t>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>360</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>742</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -2193,82 +2193,82 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5414</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -2419,72 +2419,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>342</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2532,82 +2532,82 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1592</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5471</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -2758,72 +2758,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2422</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>13,12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -2871,72 +2871,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4060</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2545</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6177</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2140</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5517</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>735</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>10924</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>34514</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>28114</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>39104</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>73,34%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>59,74%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>83,09%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>36702</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>31591</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>40946</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>75,77%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>65,22%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>37006</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30614</t>
+          <t>31054</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40672</t>
+          <t>41205</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>72670</t>
+          <t>71520</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65350</t>
+          <t>63732</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79119</t>
+          <t>78315</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,45%</t>
         </is>
       </c>
     </row>
@@ -3323,74 +3323,74 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>49093</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>49093</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>49093</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>48755</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>48755</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>48755</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>142</t>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -4118,72 +4118,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>1661</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>5474</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -4344,72 +4344,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2782</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>6902</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>2405</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>369</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>4799</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2138</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>8509</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>25,99%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>3382</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>6618</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>13,82%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -4570,72 +4570,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>24157</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>19408</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>27822</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>73,78%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>59,28%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>84,98%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>14776</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>21316</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>74,7%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>87,13%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>46818</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>40525</t>
+          <t>35849</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>52275</t>
+          <t>46766</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -4683,74 +4683,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>38059</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>38059</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>38059</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>88</t>
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,107 +4800,107 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>2949</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>8708</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -4913,47 +4913,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>1118</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>4355</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>860</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>481</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5026,82 +5026,82 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>945</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>4896</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>945</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5252,82 +5252,82 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>4335</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>962</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5365,72 +5365,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>6426</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>486</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>497</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5478,72 +5478,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2138</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>7019</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>355</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -5591,72 +5591,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>1635</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>5195</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>326</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -5704,72 +5704,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>8873</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>4384</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>16931</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>17,34%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>5091</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>1693</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>10060</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>21916</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -5817,72 +5817,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11319</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>5674</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>26466</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>27,1%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>7708</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>3049</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>13641</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>31187</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>36859</t>
+          <t>32636</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -5930,72 +5930,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>68304</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>57363</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>76411</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>69,95%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>58,74%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>100610</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>91000</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>111003</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>74234</t>
+          <t>71228</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>61482</t>
+          <t>64299</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>83199</t>
+          <t>77068</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>174844</t>
+          <t>139532</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>158244</t>
+          <t>126441</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>192435</t>
+          <t>149204</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>79,18%</t>
         </is>
       </c>
     </row>
@@ -6043,74 +6043,74 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>90791</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>90791</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>90791</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>105894</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>105894</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>105894</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>285</t>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6273,82 +6273,82 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>5674</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -6612,82 +6612,82 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>365</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>365</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6838,72 +6838,72 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>8452</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>5584</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>904</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -7064,72 +7064,72 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>1495</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>4379</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>1386</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>4556</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,32 +7139,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>745</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -7177,72 +7177,72 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>5684</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>2863</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>10571</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>5551</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>2651</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>10321</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -7290,72 +7290,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>55391</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>48783</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>60253</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>80,44%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>70,84%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>87,5%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>41519</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>36248</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>45120</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>82,64%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>58385</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>33533</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>64282</t>
+          <t>42084</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>99904</t>
+          <t>93686</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>90906</t>
+          <t>86128</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>106540</t>
+          <t>99894</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -7403,74 +7403,74 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>46778</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>46778</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>46778</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>74439</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>74439</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>74439</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>177</t>
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7633,72 +7633,72 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>2760</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>359</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -7972,82 +7972,82 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>1585</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>9258</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>23,01%</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -8198,47 +8198,47 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>3958</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>21,92%</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -8311,72 +8311,72 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>4133</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>874</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>530</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -8537,72 +8537,72 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>8712</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>12,43%</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>23,36%</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>7371</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>3538</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>7291</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>11,04%</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>4587</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>8642</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -8650,72 +8650,72 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>29455</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>24050</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>33392</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>78,97%</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>64,48%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>89,53%</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>23466</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>19021</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>26994</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>75,96%</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>61,57%</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>87,38%</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>36145</t>
+          <t>28108</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>53728</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>48530</t>
+          <t>46915</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>60707</t>
+          <t>59821</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -8763,74 +8763,74 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>32047</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>32047</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>32047</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="P75" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>40230</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>40230</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>40230</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>95</t>
@@ -8838,17 +8838,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8880,72 +8880,72 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>5178</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>10988</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>4142</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>6025</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>2506</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>12838</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -8993,72 +8993,72 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>6463</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>12190</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>367</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9068,32 +9068,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -9106,82 +9106,82 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>1915</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>5907</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
@@ -9191,12 +9191,12 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -9219,47 +9219,47 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1670</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>4568</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9294,22 +9294,22 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>325</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -9332,72 +9332,72 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>4483</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>11306</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2173</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -9445,72 +9445,72 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>7320</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>2951</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>7457</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>871</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9520,32 +9520,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -9558,72 +9558,72 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>9323</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>15785</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>11504</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>6582</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>19367</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9633,32 +9633,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>33741</t>
+          <t>30747</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -9671,72 +9671,72 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>4046</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>8711</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>6060</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>2958</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>11134</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,32 +9746,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -9784,72 +9784,72 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18712</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>11412</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>27883</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>13890</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>8746</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>20813</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>30061</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>34509</t>
+          <t>32475</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>24507</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>46630</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -9902,32 +9902,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>37003</t>
+          <t>41868</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>26887</t>
+          <t>32763</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>47411</t>
+          <t>56460</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9937,32 +9937,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>43183</t>
+          <t>38421</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>60293</t>
+          <t>48475</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9972,32 +9972,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>80186</t>
+          <t>80288</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>66135</t>
+          <t>67089</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>99516</t>
+          <t>97405</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -10010,72 +10010,72 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>257956</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>241704</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>271275</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>73,24%</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>68,63%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>77,02%</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>251670</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>236932</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>269341</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>76,66%</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>72,17%</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>82,04%</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>278698</t>
+          <t>219719</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>259784</t>
+          <t>205224</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>293464</t>
+          <t>231509</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10085,32 +10085,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>530367</t>
+          <t>477674</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>506638</t>
+          <t>457305</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>555525</t>
+          <t>496500</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>76,42%</t>
         </is>
       </c>
     </row>
@@ -10123,74 +10123,74 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
           <t>463</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>297508</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>297508</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>297508</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="P87" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>379906</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>379906</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>379906</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>965</t>
@@ -10198,17 +10198,17 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
